--- a/sample_templates/浆粕成品流水.xlsx
+++ b/sample_templates/浆粕成品流水.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -467,8 +467,10 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -519,10 +521,20 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>单价</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>业务类型</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>车间</t>
         </is>
@@ -564,12 +576,14 @@
           <t>千克</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>生产入库</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>浆粕车间</t>
         </is>
@@ -611,12 +625,14 @@
           <t>千克</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>生产入库</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>浆粕车间</t>
         </is>
@@ -658,12 +674,14 @@
           <t>千克</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>销售出库</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>浆粕车间</t>
         </is>
@@ -713,7 +731,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. 单价/金额一律留空：生产入库按工单完工成本自动回填，销售出库按月末加权价自动回填。</t>
+          <t>3. 单价/金额**留空**：生产入库按工单完工成本自动回填，销售出库按月末加权价自动回填；如手工填写则以填写为准。</t>
         </is>
       </c>
     </row>

--- a/sample_templates/浆粕成品流水.xlsx
+++ b/sample_templates/浆粕成品流水.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,9 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -83,13 +86,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -470,7 +474,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -539,6 +543,11 @@
           <t>车间</t>
         </is>
       </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -588,6 +597,11 @@
           <t>浆粕车间</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>浆粕车间7月生产入库</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -637,6 +651,11 @@
           <t>浆粕车间</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>浆粕车间7月生产入库</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -684,6 +703,11 @@
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>浆粕车间</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>浆粕车间7月销售出库</t>
         </is>
       </c>
     </row>
@@ -711,9 +735,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
